--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486454_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486454_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. MARTINEZ CLARIANA</t>
+          <t>D. KRISTENSEN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.386</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7635</v>
+        <v>0.8978</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.3775</v>
+        <v>-0.3579</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.573</v>
+        <v>-0.1208</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5962</v>
+        <v>1.2681</v>
       </c>
       <c r="I2" t="n">
-        <v>-4.1692</v>
+        <v>-1.3889</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5222</v>
+        <v>0.186</v>
       </c>
       <c r="K2" t="n">
-        <v>1.229</v>
+        <v>0.1095</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.7068</v>
+        <v>0.0765</v>
       </c>
       <c r="M2" t="n">
-        <v>-4.0952</v>
+        <v>-0.3068</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.6328</v>
+        <v>1.1586</v>
       </c>
       <c r="O2" t="n">
-        <v>-3.4624</v>
+        <v>-1.4654</v>
       </c>
       <c r="P2" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2362</v>
+        <v>-0.0141</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2139</v>
+        <v>-0.4182</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0224</v>
+        <v>0.4041</v>
       </c>
       <c r="V2" t="n">
-        <v>2.4552</v>
+        <v>-0.1952</v>
       </c>
       <c r="W2" t="n">
-        <v>2.4552</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. KRISTENSEN</t>
+          <t>A. MARTINEZ CLARIANA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2354</v>
+        <v>0.5093</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5625</v>
+        <v>2.7635</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3271</v>
+        <v>-2.2542</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1208</v>
+        <v>-3.573</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2681</v>
+        <v>0.5962</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.3889</v>
+        <v>-4.1692</v>
       </c>
       <c r="J3" t="n">
-        <v>0.186</v>
+        <v>0.5222</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1095</v>
+        <v>1.229</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0765</v>
+        <v>-0.7068</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3068</v>
+        <v>-4.0952</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1586</v>
+        <v>-0.6328</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.4654</v>
+        <v>-3.4624</v>
       </c>
       <c r="P3" t="n">
-        <v>0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3186</v>
+        <v>-0.113</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.2139</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4349</v>
+        <v>0.1009</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1952</v>
+        <v>2.4552</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13</v>
+        <v>2.4552</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2319</v>
+        <v>0.1439</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.7239</v>
+        <v>-1.8105</v>
       </c>
       <c r="F4" t="n">
-        <v>1.492</v>
+        <v>1.9543</v>
       </c>
       <c r="G4" t="n">
         <v>0.6363</v>
@@ -766,13 +766,13 @@
         <v>1.305</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0857</v>
+        <v>-0.7099</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4194</v>
+        <v>-0.5059</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6663</v>
+        <v>-0.204</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.396</v>
+        <v>-0.1108</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.8157</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9882</v>
+        <v>-0.9265</v>
       </c>
       <c r="G5" t="n">
         <v>-1.1256</v>
@@ -844,13 +844,13 @@
         <v>1.5225</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1834</v>
+        <v>-0.8983</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.822</v>
+        <v>-0.5984</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3615</v>
+        <v>-0.2998</v>
       </c>
       <c r="V5" t="n">
         <v>0.3904</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.1612</v>
+        <v>-1.8247</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4091</v>
+        <v>-0.9801</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7522</v>
+        <v>-0.8446</v>
       </c>
       <c r="G6" t="n">
         <v>-2.0873</v>
@@ -922,13 +922,13 @@
         <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4352</v>
+        <v>-1.0986</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1644</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2708</v>
+        <v>-0.3632</v>
       </c>
       <c r="V6" t="n">
         <v>0.7088</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. PAUKSTÈ</t>
+          <t>T. NASPLER PERAIRE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.1418</v>
+        <v>-3.586</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9358</v>
+        <v>-4.9055</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.0776</v>
+        <v>1.3195</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.1575</v>
+        <v>-1.3347</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.3478</v>
+        <v>0.8758</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.8097</v>
+        <v>-2.2105</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6822</v>
+        <v>-0.976</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7205</v>
+        <v>-0.2309</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0382</v>
+        <v>-0.7451</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.4753</v>
+        <v>-0.3587</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.6274</v>
+        <v>1.1067</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.8479</v>
+        <v>-1.4654</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5225</v>
+        <v>-1.305</v>
       </c>
       <c r="Q7" t="n">
+        <v>-3.2626</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.9576</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.7511</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.6669</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.08409999999999999</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-0.1952</v>
+      </c>
+      <c r="W7" t="n">
         <v>0</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.5225</v>
-      </c>
-      <c r="S7" t="n">
-        <v>-0.2808</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-0.0769</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-0.2039</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-0.226</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.695</v>
-      </c>
       <c r="X7" t="n">
-        <v>-1.921</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. VAN ZEGEREN</t>
+          <t>J. PAUKSTÈ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.7329</v>
+        <v>-3.7361</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3032</v>
+        <v>0.5573</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4297</v>
+        <v>-4.2934</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4938</v>
+        <v>-4.1575</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2339</v>
+        <v>-2.3478</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2599</v>
+        <v>-1.8097</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9661</v>
+        <v>-0.6822</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.0426</v>
+        <v>-0.7205</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0765</v>
+        <v>0.0382</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5276999999999999</v>
+        <v>-3.4753</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8087</v>
+        <v>-1.6274</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.3364</v>
+        <v>-1.8479</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2175</v>
+        <v>1.5225</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S8" t="n">
-        <v>0.173</v>
+        <v>-0.8751</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1202</v>
+        <v>-0.4554</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0529</v>
+        <v>-0.4197</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.6297</v>
+        <v>-0.226</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3698</v>
+        <v>1.695</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.2599</v>
+        <v>-1.921</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. NASPLER PERAIRE</t>
+          <t>J. VAN ZEGEREN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.7684</v>
+        <v>-4.043</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.3345</v>
+        <v>-2.6133</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5661</v>
+        <v>-1.4297</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3347</v>
+        <v>-1.4938</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8758</v>
+        <v>-0.2339</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.2105</v>
+        <v>-1.2599</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.976</v>
+        <v>-0.9661</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2309</v>
+        <v>-1.0426</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7451</v>
+        <v>0.0765</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3587</v>
+        <v>-0.5276999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>1.1067</v>
+        <v>0.8087</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4654</v>
+        <v>-1.3364</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.305</v>
+        <v>0.2175</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9576</v>
+        <v>1.305</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9335</v>
+        <v>-0.137</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0959</v>
+        <v>-0.1899</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1625</v>
+        <v>0.0529</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1952</v>
+        <v>-2.6297</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1952</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.342</v>
+        <v>-5.7261</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9942</v>
+        <v>-3.3475</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3478</v>
+        <v>-2.3786</v>
       </c>
       <c r="G10" t="n">
         <v>-5.0668</v>
@@ -1234,13 +1234,13 @@
         <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.202</v>
+        <v>-0.5861</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2572</v>
+        <v>-0.0961</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4592</v>
+        <v>-0.49</v>
       </c>
       <c r="V10" t="n">
         <v>-1.1607</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.4108</v>
+        <v>-5.9638</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5291</v>
+        <v>-2.0821</v>
       </c>
       <c r="F11" t="n">
         <v>-3.8817</v>
@@ -1312,10 +1312,10 @@
         <v>1.305</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6355</v>
+        <v>-1.1885</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2329</v>
+        <v>-0.7859</v>
       </c>
       <c r="U11" t="n">
         <v>-0.4026</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.3332</v>
+        <v>-7.072</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5663</v>
+        <v>-2.2743</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.7668</v>
+        <v>-4.7977</v>
       </c>
       <c r="G12" t="n">
         <v>-4.4201</v>
@@ -1390,13 +1390,13 @@
         <v>0.87</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3821</v>
+        <v>-1.1209</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0274</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3546</v>
+        <v>-0.3854</v>
       </c>
       <c r="V12" t="n">
         <v>-0.226</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-31.8968</v>
+        <v>-30.8695</v>
       </c>
       <c r="E13" t="n">
-        <v>-14.0063</v>
+        <v>-12.979</v>
       </c>
       <c r="F13" t="n">
         <v>-17.8905</v>
@@ -1468,16 +1468,16 @@
         <v>15.2253</v>
       </c>
       <c r="S13" t="n">
-        <v>-8.52</v>
+        <v>-7.492599999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-6.428900000000001</v>
+        <v>-5.401400000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.091</v>
+        <v>-2.0909</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9556000000000002</v>
+        <v>0.9555999999999998</v>
       </c>
       <c r="W13" t="n">
         <v>8.885899999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.421</v>
+        <v>7.5558</v>
       </c>
       <c r="E14" t="n">
-        <v>4.7975</v>
+        <v>4.6858</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6235</v>
+        <v>2.87</v>
       </c>
       <c r="G14" t="n">
         <v>5.1962</v>
@@ -1546,13 +1546,13 @@
         <v>1.9576</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4624</v>
+        <v>0.5972</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1406</v>
+        <v>0.0288</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3218</v>
+        <v>0.5684</v>
       </c>
       <c r="V14" t="n">
         <v>-0.1952</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.8017</v>
+        <v>7.2257</v>
       </c>
       <c r="E15" t="n">
-        <v>5.0461</v>
+        <v>5.7167</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7556</v>
+        <v>1.509</v>
       </c>
       <c r="G15" t="n">
         <v>5.0997</v>
@@ -1624,13 +1624,13 @@
         <v>0.87</v>
       </c>
       <c r="S15" t="n">
-        <v>0.267</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.0024</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9399</v>
+        <v>0.6934</v>
       </c>
       <c r="V15" t="n">
         <v>0.5649999999999999</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.0463</v>
+        <v>6.5588</v>
       </c>
       <c r="E16" t="n">
-        <v>4.8101</v>
+        <v>4.9218</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2362</v>
+        <v>1.6369</v>
       </c>
       <c r="G16" t="n">
         <v>7.0101</v>
@@ -1702,13 +1702,13 @@
         <v>1.7401</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6012</v>
+        <v>1.1137</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2211</v>
+        <v>0.3329</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3801</v>
+        <v>0.7808</v>
       </c>
       <c r="V16" t="n">
         <v>-1.13</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.8104</v>
+        <v>4.5156</v>
       </c>
       <c r="E17" t="n">
-        <v>3.3673</v>
+        <v>2.4733</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4431</v>
+        <v>2.0424</v>
       </c>
       <c r="G17" t="n">
         <v>2.1821</v>
@@ -1780,13 +1780,13 @@
         <v>1.5225</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1084</v>
+        <v>1.8137</v>
       </c>
       <c r="T17" t="n">
-        <v>1.7797</v>
+        <v>0.8857</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3287</v>
+        <v>0.928</v>
       </c>
       <c r="V17" t="n">
         <v>2.2599</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. KORSANTIA</t>
+          <t>I. ARROYO VARELA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.7291</v>
+        <v>3.3714</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2718</v>
+        <v>2.2162</v>
       </c>
       <c r="F18" t="n">
-        <v>3.4573</v>
+        <v>1.1551</v>
       </c>
       <c r="G18" t="n">
-        <v>1.02</v>
+        <v>3.9705</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.961</v>
+        <v>0.6994</v>
       </c>
       <c r="I18" t="n">
-        <v>1.981</v>
+        <v>3.2711</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3627</v>
+        <v>3.1307</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.9577</v>
+        <v>0.2222</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3204</v>
+        <v>2.9086</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6573</v>
+        <v>0.8398</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0033</v>
+        <v>0.4772</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6606</v>
+        <v>0.3626</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6525</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="S18" t="n">
-        <v>2.9919</v>
+        <v>0.5308</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9542</v>
+        <v>0.173</v>
       </c>
       <c r="U18" t="n">
-        <v>2.0377</v>
+        <v>0.3578</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3698</v>
+        <v>-1.13</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.7602</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. ARROYO VARELA</t>
+          <t>G. KORSANTIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.5236</v>
+        <v>2.4613</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7692</v>
+        <v>-0.287</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7544</v>
+        <v>2.7484</v>
       </c>
       <c r="G19" t="n">
-        <v>3.9705</v>
+        <v>1.02</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6994</v>
+        <v>-0.961</v>
       </c>
       <c r="I19" t="n">
-        <v>3.2711</v>
+        <v>1.981</v>
       </c>
       <c r="J19" t="n">
-        <v>3.1307</v>
+        <v>0.3627</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2222</v>
+        <v>-0.9577</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9086</v>
+        <v>1.3204</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8398</v>
+        <v>0.6573</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4772</v>
+        <v>-0.0033</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3626</v>
+        <v>0.6606</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3169</v>
+        <v>1.7241</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.274</v>
+        <v>0.3954</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0429</v>
+        <v>1.3288</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.13</v>
+        <v>0.3698</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.13</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. MOTOS CABODEVILLA</t>
+          <t>A. ZUBIZARRETA ARANBARRI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.239</v>
+        <v>2.4007</v>
       </c>
       <c r="E20" t="n">
-        <v>1.9798</v>
+        <v>0.0486</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2592</v>
+        <v>2.3521</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4099</v>
+        <v>0.4298</v>
       </c>
       <c r="H20" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.0029</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4008</v>
+        <v>0.4327</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6952</v>
+        <v>-0.3279</v>
       </c>
       <c r="K20" t="n">
-        <v>0.657</v>
+        <v>-0.1</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0382</v>
+        <v>-0.2279</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2854</v>
+        <v>0.7577</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6479</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3626</v>
+        <v>0.6606</v>
       </c>
       <c r="P20" t="n">
-        <v>0.435</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
+        <v>-1.0875</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.0875</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.8409</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.5068</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X20" t="n">
         <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.5894</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.2846</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0.3047</v>
-      </c>
-      <c r="V20" t="n">
-        <v>-0.1952</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>-0.1952</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. ZUBIZARRETA ARANBARRI</t>
+          <t>J. NICOLAU ALEDON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.7995</v>
+        <v>2.0942</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3984</v>
+        <v>2.9052</v>
       </c>
       <c r="F21" t="n">
-        <v>2.1979</v>
+        <v>-0.8110000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4298</v>
+        <v>1.6612</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0029</v>
+        <v>0.8818</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4327</v>
+        <v>0.7793</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3279</v>
+        <v>1.7824</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1</v>
+        <v>1.5147</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.2279</v>
+        <v>0.2677</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7577</v>
+        <v>-0.1213</v>
       </c>
       <c r="N21" t="n">
-        <v>0.09710000000000001</v>
+        <v>-0.6328</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6606</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="P21" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="Q21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-1.0875</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2397</v>
+        <v>0.128</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.113</v>
+        <v>-0.0072</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3527</v>
+        <v>0.1352</v>
       </c>
       <c r="V21" t="n">
-        <v>1.13</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W21" t="n">
         <v>1.13</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. NICOLAU ALEDON</t>
+          <t>M. MOTOS CABODEVILLA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.4507</v>
+        <v>1.4452</v>
       </c>
       <c r="E22" t="n">
-        <v>2.5699</v>
+        <v>1.3093</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1193</v>
+        <v>0.1359</v>
       </c>
       <c r="G22" t="n">
-        <v>1.6612</v>
+        <v>0.4099</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8818</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7793</v>
+        <v>0.4008</v>
       </c>
       <c r="J22" t="n">
-        <v>1.7824</v>
+        <v>0.6952</v>
       </c>
       <c r="K22" t="n">
-        <v>1.5147</v>
+        <v>0.657</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2677</v>
+        <v>0.0382</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1213</v>
+        <v>-0.2854</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6328</v>
+        <v>-0.6479</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.3626</v>
       </c>
       <c r="P22" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5155</v>
+        <v>0.7955</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3425</v>
+        <v>0.6141</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.173</v>
+        <v>0.1815</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.1952</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.695</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.3472</v>
+        <v>-1.7171</v>
       </c>
       <c r="E23" t="n">
         <v>-2.8298</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4827</v>
+        <v>1.1128</v>
       </c>
       <c r="G23" t="n">
         <v>-0.6778</v>
@@ -2248,13 +2248,13 @@
         <v>1.305</v>
       </c>
       <c r="S23" t="n">
-        <v>1.1354</v>
+        <v>0.7655</v>
       </c>
       <c r="T23" t="n">
         <v>-0.0649</v>
       </c>
       <c r="U23" t="n">
-        <v>1.2002</v>
+        <v>0.8304</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9347</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.5772</v>
+        <v>-4.0147</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.493</v>
+        <v>-3.2695</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0843</v>
+        <v>-0.7452</v>
       </c>
       <c r="G24" t="n">
         <v>0.2058</v>
@@ -2326,13 +2326,13 @@
         <v>0.6525</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0429</v>
+        <v>-0.4804</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.822</v>
+        <v>-0.5984</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.221</v>
+        <v>0.1181</v>
       </c>
       <c r="V24" t="n">
         <v>-1.13</v>
@@ -2362,10 +2362,10 @@
         <v>31.89689999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>17.8905</v>
+        <v>17.8906</v>
       </c>
       <c r="F25" t="n">
-        <v>14.0063</v>
+        <v>14.0064</v>
       </c>
       <c r="G25" t="n">
         <v>26.5075</v>
@@ -2404,16 +2404,16 @@
         <v>13.0502</v>
       </c>
       <c r="S25" t="n">
-        <v>8.520100000000001</v>
+        <v>8.520000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>2.090899999999999</v>
+        <v>2.0911</v>
       </c>
       <c r="U25" t="n">
-        <v>6.4289</v>
+        <v>6.4292</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.9553999999999997</v>
+        <v>-0.9553999999999999</v>
       </c>
       <c r="W25" t="n">
         <v>7.930499999999999</v>
